--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,9 +607,35 @@
         <v>2963070.11</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2025-03-10 22:30:57</v>
+      </c>
+      <c r="B9">
+        <v>300</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="str">
+        <v>54821.57</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2850721.64</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -633,9 +633,87 @@
         <v>2850721.64</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2025-03-12 11:09:20</v>
+      </c>
+      <c r="B10">
+        <v>300</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10" t="str">
+        <v>33375.51</v>
+      </c>
+      <c r="H10" t="str">
+        <v>1735526.64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2025-03-12 12:03:34</v>
+      </c>
+      <c r="B11">
+        <v>200</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" t="str">
+        <v>24440.16</v>
+      </c>
+      <c r="H11" t="str">
+        <v>1270888.54</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2025-03-12 12:17:49</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12" t="str">
+        <v>68825.38</v>
+      </c>
+      <c r="H12" t="str">
+        <v>3578919.72</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/operations.xlsx
+++ b/operations.xlsx
@@ -397,121 +397,157 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Date &amp; Time</v>
+        <v>📆 Date &amp; Time</v>
       </c>
       <c r="B1" t="str">
-        <v>Required construction area (square meters)</v>
+        <v>📏  construction area (m²)</v>
       </c>
       <c r="C1" t="str">
-        <v>Building type (1: Residential, 2: Pump Station, 3: Bridge)</v>
+        <v>🏠  building type (1: Residential, 2: Pump Station, 3: Bridge)</v>
       </c>
       <c r="D1" t="str">
-        <v>Number of allowed floors</v>
+        <v>🏢  number of floors</v>
       </c>
       <c r="E1" t="str">
-        <v>Permit duration (years)</v>
+        <v>📅  permit duration (years)</v>
       </c>
       <c r="F1" t="str">
-        <v>Distance from nearest waterway (meters)</v>
+        <v>🌊  distance from waterway (m)</v>
       </c>
       <c r="G1" t="str">
-        <v>Estimated house price (USD)</v>
+        <v>🛠️  soil type (1: Rocky, 2: Clay, 3: Sandy)</v>
       </c>
       <c r="H1" t="str">
-        <v>Estimated house price (EGP)</v>
+        <v>💰  material cost per m²</v>
+      </c>
+      <c r="I1" t="str">
+        <v>📆  application year</v>
+      </c>
+      <c r="J1" t="str">
+        <v>💰  house price (USD)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>💰  house price (EGP)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-03-08 21:32:41</v>
+        <v>2025-03-13 20:47:32</v>
       </c>
       <c r="B2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2" t="str">
-        <v>90280.44</v>
-      </c>
-      <c r="H2" t="str">
-        <v>4694582.64</v>
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>2022</v>
+      </c>
+      <c r="J2" t="str">
+        <v>534.31</v>
+      </c>
+      <c r="K2" t="str">
+        <v>27073.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-03-08 21:37:58</v>
+        <v>2025-03-13 20:48:30</v>
       </c>
       <c r="B3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>60</v>
-      </c>
-      <c r="G3" t="str">
-        <v>72485.95</v>
-      </c>
-      <c r="H3" t="str">
-        <v>3769269.61</v>
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3">
+        <v>2025</v>
+      </c>
+      <c r="J3" t="str">
+        <v>889.13</v>
+      </c>
+      <c r="K3" t="str">
+        <v>45052.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-03-08 21:40:27</v>
+        <v>2025-03-13 20:52:16</v>
       </c>
       <c r="B4">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>100</v>
       </c>
-      <c r="G4" t="str">
-        <v>86722.94</v>
-      </c>
-      <c r="H4" t="str">
-        <v>4509592.72</v>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4">
+        <v>2025</v>
+      </c>
+      <c r="J4" t="str">
+        <v>767.53</v>
+      </c>
+      <c r="K4" t="str">
+        <v>38890.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-03-09 08:19:17</v>
+        <v>2025-03-13 20:57:37</v>
       </c>
       <c r="B5">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -520,200 +556,237 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5" t="str">
-        <v>57669.66</v>
-      </c>
-      <c r="H5" t="str">
-        <v>2998822.29</v>
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>2022</v>
+      </c>
+      <c r="J5" t="str">
+        <v>433.33</v>
+      </c>
+      <c r="K5" t="str">
+        <v>21956.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-03-09 08:20:19</v>
+        <v>2025-03-13 21:02:52</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6" t="str">
-        <v>62707.64</v>
-      </c>
-      <c r="H6" t="str">
-        <v>3260797.14</v>
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>2025</v>
+      </c>
+      <c r="J6" t="str">
+        <v>392.27</v>
+      </c>
+      <c r="K6" t="str">
+        <v>19876.40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-03-09 10:56:28</v>
+        <v>2025-03-13 21:07:04</v>
       </c>
       <c r="B7">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>100</v>
       </c>
-      <c r="G7" t="str">
-        <v>87366.03</v>
-      </c>
-      <c r="H7" t="str">
-        <v>4543033.34</v>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7">
+        <v>2025</v>
+      </c>
+      <c r="J7" t="str">
+        <v>606.48</v>
+      </c>
+      <c r="K7" t="str">
+        <v>30730.30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-03-09 11:00:53</v>
+        <v>2025-03-13 21:10:59</v>
       </c>
       <c r="B8">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="str">
-        <v>56982.12</v>
-      </c>
-      <c r="H8" t="str">
-        <v>2963070.11</v>
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <v>2025</v>
+      </c>
+      <c r="J8" t="str">
+        <v>378.17</v>
+      </c>
+      <c r="K8" t="str">
+        <v>19161.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-03-10 22:30:57</v>
+        <v>2025-03-13 21:12:40</v>
       </c>
       <c r="B9">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9" t="str">
-        <v>54821.57</v>
-      </c>
-      <c r="H9" t="str">
-        <v>2850721.64</v>
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>200</v>
+      </c>
+      <c r="I9">
+        <v>2025</v>
+      </c>
+      <c r="J9" t="str">
+        <v>435.43</v>
+      </c>
+      <c r="K9" t="str">
+        <v>22062.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-03-12 11:09:20</v>
+        <v>2025-03-13 21:14:00</v>
       </c>
       <c r="B10">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F10">
         <v>20</v>
       </c>
-      <c r="G10" t="str">
-        <v>33375.51</v>
-      </c>
-      <c r="H10" t="str">
-        <v>1735526.64</v>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>2025</v>
+      </c>
+      <c r="J10" t="str">
+        <v>421.77</v>
+      </c>
+      <c r="K10" t="str">
+        <v>21371.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-03-12 12:03:34</v>
+        <v>2025-03-13 21:18:26</v>
       </c>
       <c r="B11">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>20</v>
-      </c>
-      <c r="G11" t="str">
-        <v>24440.16</v>
-      </c>
-      <c r="H11" t="str">
-        <v>1270888.54</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>2025-03-12 12:17:49</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>40</v>
-      </c>
-      <c r="G12" t="str">
-        <v>68825.38</v>
-      </c>
-      <c r="H12" t="str">
-        <v>3578919.72</v>
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>90</v>
+      </c>
+      <c r="I11">
+        <v>2025</v>
+      </c>
+      <c r="J11" t="str">
+        <v>386.62</v>
+      </c>
+      <c r="K11" t="str">
+        <v>19590.15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>